--- a/artfynd/A 11308-2021 artfynd.xlsx
+++ b/artfynd/A 11308-2021 artfynd.xlsx
@@ -717,7 +717,7 @@
         <v>619341</v>
       </c>
       <c r="R2" t="n">
-        <v>6878902</v>
+        <v>6878903</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -818,7 +818,7 @@
         <v>619341</v>
       </c>
       <c r="R3" t="n">
-        <v>6878902</v>
+        <v>6878903</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129179158</v>
+        <v>129178837</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619301</v>
+        <v>619341</v>
       </c>
       <c r="R4" t="n">
-        <v>6879066</v>
+        <v>6878903</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129178837</v>
+        <v>129179158</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619341</v>
+        <v>619301</v>
       </c>
       <c r="R5" t="n">
-        <v>6878902</v>
+        <v>6879066</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 11308-2021 artfynd.xlsx
+++ b/artfynd/A 11308-2021 artfynd.xlsx
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129178837</v>
+        <v>129179158</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619341</v>
+        <v>619301</v>
       </c>
       <c r="R4" t="n">
-        <v>6878903</v>
+        <v>6879066</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129179158</v>
+        <v>129178837</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619301</v>
+        <v>619341</v>
       </c>
       <c r="R5" t="n">
-        <v>6879066</v>
+        <v>6878903</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 11308-2021 artfynd.xlsx
+++ b/artfynd/A 11308-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129178796</v>
       </c>
       <c r="B2" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129178792</v>
       </c>
       <c r="B3" t="n">
-        <v>57853</v>
+        <v>57855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129179158</v>
+        <v>129178837</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57722</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619301</v>
+        <v>619341</v>
       </c>
       <c r="R4" t="n">
-        <v>6879066</v>
+        <v>6878903</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129178837</v>
+        <v>129179158</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619341</v>
+        <v>619301</v>
       </c>
       <c r="R5" t="n">
-        <v>6878903</v>
+        <v>6879066</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 11308-2021 artfynd.xlsx
+++ b/artfynd/A 11308-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129178796</v>
       </c>
       <c r="B2" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129178792</v>
       </c>
       <c r="B3" t="n">
-        <v>57855</v>
+        <v>57857</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129178837</v>
       </c>
       <c r="B4" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>129179158</v>
       </c>
       <c r="B5" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11308-2021 artfynd.xlsx
+++ b/artfynd/A 11308-2021 artfynd.xlsx
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129178837</v>
+        <v>129179158</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619341</v>
+        <v>619301</v>
       </c>
       <c r="R4" t="n">
-        <v>6878903</v>
+        <v>6879066</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129179158</v>
+        <v>129178837</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619301</v>
+        <v>619341</v>
       </c>
       <c r="R5" t="n">
-        <v>6879066</v>
+        <v>6878903</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 11308-2021 artfynd.xlsx
+++ b/artfynd/A 11308-2021 artfynd.xlsx
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129179158</v>
+        <v>129178837</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619301</v>
+        <v>619341</v>
       </c>
       <c r="R4" t="n">
-        <v>6879066</v>
+        <v>6878903</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129178837</v>
+        <v>129179158</v>
       </c>
       <c r="B5" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619341</v>
+        <v>619301</v>
       </c>
       <c r="R5" t="n">
-        <v>6878903</v>
+        <v>6879066</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 11308-2021 artfynd.xlsx
+++ b/artfynd/A 11308-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129178796</v>
       </c>
       <c r="B2" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129178792</v>
       </c>
       <c r="B3" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129178837</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>129179158</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11308-2021 artfynd.xlsx
+++ b/artfynd/A 11308-2021 artfynd.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
